--- a/data/Ficha_15_DL1153_202605_Mamografia.xlsx
+++ b/data/Ficha_15_DL1153_202605_Mamografia.xlsx
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="108" r:id="rId3"/>
+    <pivotCache cacheId="119" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -97,7 +97,7 @@
     <t>PERIODO: ENERO - MAYO 2026</t>
   </si>
   <si>
-    <t>FUENTE: HISMINSA: 17/05/2026</t>
+    <t>FUENTE: HISMINSA: 24/05/2026</t>
   </si>
 </sst>
 </file>
@@ -288,12 +288,6 @@
   </cellStyles>
   <dxfs count="40">
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
@@ -368,6 +362,12 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <font>
@@ -526,6 +526,12 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -600,12 +606,6 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -621,7 +621,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.522273032409" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="5">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.525317824075" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="5">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -670,7 +670,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5760" maxValue="5760"/>
     </cacheField>
     <cacheField name="NUMERADOR" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="58"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="21" maxValue="58"/>
     </cacheField>
     <cacheField name="Indicador" numFmtId="0" formula="NUMERADOR/DENOMINADOR" databaseField="0"/>
   </cacheFields>
@@ -742,226 +742,13 @@
     <x v="0"/>
     <x v="0"/>
     <n v="5760"/>
-    <n v="0"/>
+    <n v="21"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica12" cacheId="108" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="J8:N13" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="11">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="1">
-        <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="0"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de DENOMINADOR" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de NUMERADOR" fld="9" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Indicador" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="37">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="29">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="27">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0" selected="0"/>
-          <reference field="1" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica11" cacheId="108" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica11" cacheId="119" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A8:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="4" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
@@ -1048,7 +835,7 @@
     <dataField name="Suma de Indicador" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="39">
+    <format dxfId="27">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -1057,11 +844,224 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="26">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica12" cacheId="119" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="J8:N13" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de DENOMINADOR" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de NUMERADOR" fld="9" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Indicador" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="39">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="1">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -1520,10 +1520,10 @@
         <v>5760</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G9" s="8">
-        <v>0</v>
+        <v>3.6458333333333334E-3</v>
       </c>
       <c r="J9">
         <v>2026</v>
@@ -1549,10 +1549,10 @@
         <v>5760</v>
       </c>
       <c r="F10" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G10" s="8">
-        <v>0</v>
+        <v>3.6458333333333334E-3</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1603,10 +1603,10 @@
         <v>5760</v>
       </c>
       <c r="M13" s="7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N13" s="9">
-        <v>0</v>
+        <v>3.6458333333333334E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1821,7 +1821,7 @@
         <v>5760</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
